--- a/artfynd/A 64564-2021 artfynd.xlsx
+++ b/artfynd/A 64564-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64564-2021 artfynd.xlsx
+++ b/artfynd/A 64564-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -806,6 +806,503 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121993903</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90272</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ånö, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>681977</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6683614</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hökhuvud</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121992762</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56569</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ånö, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>681555</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6683434</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hökhuvud</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121993095</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90498</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norrskedika, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>681555</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6683434</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hökhuvud</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121994071</v>
+      </c>
+      <c r="B6" t="n">
+        <v>105205</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ånö, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>681999</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6683651</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hökhuvud</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64564-2021 artfynd.xlsx
+++ b/artfynd/A 64564-2021 artfynd.xlsx
@@ -809,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121993903</v>
+        <v>121994071</v>
       </c>
       <c r="B3" t="n">
-        <v>90272</v>
+        <v>105223</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,38 +821,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5754</v>
+        <v>224098</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -860,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>681977</v>
+        <v>681999</v>
       </c>
       <c r="R3" t="n">
-        <v>6683614</v>
+        <v>6683651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -933,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121992762</v>
+        <v>121993095</v>
       </c>
       <c r="B4" t="n">
-        <v>56569</v>
+        <v>90512</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,39 +950,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ånö, Upl</t>
+          <t>Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -991,7 +991,7 @@
         <v>6683434</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,6 +1039,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1057,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121993095</v>
+        <v>121993903</v>
       </c>
       <c r="B5" t="n">
-        <v>90498</v>
+        <v>90286</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,30 +1070,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>5754</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1104,14 +1105,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrskedika, Upl</t>
+          <t>Ånö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>681555</v>
+        <v>681977</v>
       </c>
       <c r="R5" t="n">
-        <v>6683434</v>
+        <v>6683614</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1153,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,10 +1182,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121994071</v>
+        <v>121992762</v>
       </c>
       <c r="B6" t="n">
-        <v>105205</v>
+        <v>56577</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1197,35 +1198,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224098</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1233,13 +1234,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>681999</v>
+        <v>681555</v>
       </c>
       <c r="R6" t="n">
-        <v>6683651</v>
+        <v>6683434</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1268,7 +1269,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1278,7 +1279,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,7 +1288,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64564-2021 artfynd.xlsx
+++ b/artfynd/A 64564-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -809,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121994071</v>
+        <v>121993095</v>
       </c>
       <c r="B3" t="n">
-        <v>105223</v>
+        <v>90514</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,46 +825,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224098</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ånö, Upl</t>
+          <t>Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>681999</v>
+        <v>681555</v>
       </c>
       <c r="R3" t="n">
-        <v>6683651</v>
+        <v>6683434</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -906,7 +905,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121993095</v>
+        <v>121992762</v>
       </c>
       <c r="B4" t="n">
-        <v>90512</v>
+        <v>56577</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,38 +949,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrskedika, Upl</t>
+          <t>Ånö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -991,7 +991,7 @@
         <v>6683434</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +1039,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1061,7 +1060,7 @@
         <v>121993903</v>
       </c>
       <c r="B5" t="n">
-        <v>90286</v>
+        <v>90288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1182,10 +1181,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121992762</v>
+        <v>121994071</v>
       </c>
       <c r="B6" t="n">
-        <v>56577</v>
+        <v>105225</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1198,35 +1197,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>224098</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1234,13 +1233,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>681555</v>
+        <v>681999</v>
       </c>
       <c r="R6" t="n">
-        <v>6683434</v>
+        <v>6683651</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1269,7 +1268,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1279,7 +1278,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,6 +1287,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1303,6 +1303,130 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122121136</v>
+      </c>
+      <c r="B7" t="n">
+        <v>90289</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norrskedika, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>681976</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6683615</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hökhuvud</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64564-2021 artfynd.xlsx
+++ b/artfynd/A 64564-2021 artfynd.xlsx
@@ -809,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121992762</v>
+        <v>121993903</v>
       </c>
       <c r="B3" t="n">
-        <v>56584</v>
+        <v>90323</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,39 +821,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>5754</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -861,13 +860,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>681555</v>
+        <v>681977</v>
       </c>
       <c r="R3" t="n">
-        <v>6683434</v>
+        <v>6683614</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -896,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -906,7 +905,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,6 +914,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -933,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121993903</v>
+        <v>121992762</v>
       </c>
       <c r="B4" t="n">
-        <v>90323</v>
+        <v>56584</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,38 +945,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5754</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -984,13 +985,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>681977</v>
+        <v>681555</v>
       </c>
       <c r="R4" t="n">
-        <v>6683614</v>
+        <v>6683434</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1019,7 +1020,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,7 +1030,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,7 +1039,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1057,10 +1057,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121993095</v>
+        <v>121994071</v>
       </c>
       <c r="B5" t="n">
-        <v>90549</v>
+        <v>105267</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1073,45 +1073,46 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>224098</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrskedika, Upl</t>
+          <t>Ånö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>681555</v>
+        <v>681999</v>
       </c>
       <c r="R5" t="n">
-        <v>6683434</v>
+        <v>6683651</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1143,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1153,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,10 +1182,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121994071</v>
+        <v>121993095</v>
       </c>
       <c r="B6" t="n">
-        <v>105267</v>
+        <v>90549</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1197,46 +1198,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224098</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ånö, Upl</t>
+          <t>Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>681999</v>
+        <v>681555</v>
       </c>
       <c r="R6" t="n">
-        <v>6683651</v>
+        <v>6683434</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 64564-2021 artfynd.xlsx
+++ b/artfynd/A 64564-2021 artfynd.xlsx
@@ -809,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121993903</v>
+        <v>121994071</v>
       </c>
       <c r="B3" t="n">
-        <v>90323</v>
+        <v>105277</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,38 +821,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5754</v>
+        <v>224098</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -860,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>681977</v>
+        <v>681999</v>
       </c>
       <c r="R3" t="n">
-        <v>6683614</v>
+        <v>6683651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -933,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121992762</v>
+        <v>121993095</v>
       </c>
       <c r="B4" t="n">
-        <v>56584</v>
+        <v>90559</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,39 +950,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ånö, Upl</t>
+          <t>Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -991,7 +991,7 @@
         <v>6683434</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,6 +1039,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1057,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121994071</v>
+        <v>121992762</v>
       </c>
       <c r="B5" t="n">
-        <v>105267</v>
+        <v>56584</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1073,35 +1074,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224098</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1109,13 +1110,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>681999</v>
+        <v>681555</v>
       </c>
       <c r="R5" t="n">
-        <v>6683651</v>
+        <v>6683434</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,7 +1145,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,7 +1155,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,7 +1164,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121993095</v>
+        <v>121993903</v>
       </c>
       <c r="B6" t="n">
-        <v>90549</v>
+        <v>90333</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1194,30 +1194,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>5754</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1229,14 +1229,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norrskedika, Upl</t>
+          <t>Ånö, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>681555</v>
+        <v>681977</v>
       </c>
       <c r="R6" t="n">
-        <v>6683434</v>
+        <v>6683614</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,7 +1268,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1309,7 +1309,7 @@
         <v>122121136</v>
       </c>
       <c r="B7" t="n">
-        <v>90323</v>
+        <v>90333</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 64564-2021 artfynd.xlsx
+++ b/artfynd/A 64564-2021 artfynd.xlsx
@@ -1058,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121992762</v>
+        <v>121993903</v>
       </c>
       <c r="B5" t="n">
-        <v>56584</v>
+        <v>90333</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,39 +1070,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>5754</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1110,13 +1109,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>681555</v>
+        <v>681977</v>
       </c>
       <c r="R5" t="n">
-        <v>6683434</v>
+        <v>6683614</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1145,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1155,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,6 +1163,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1182,10 +1182,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121993903</v>
+        <v>121992762</v>
       </c>
       <c r="B6" t="n">
-        <v>90333</v>
+        <v>56584</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1194,38 +1194,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5754</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1233,13 +1234,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>681977</v>
+        <v>681555</v>
       </c>
       <c r="R6" t="n">
-        <v>6683614</v>
+        <v>6683434</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1268,7 +1269,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1278,7 +1279,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,7 +1288,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64564-2021 artfynd.xlsx
+++ b/artfynd/A 64564-2021 artfynd.xlsx
@@ -809,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121994071</v>
+        <v>121993095</v>
       </c>
       <c r="B3" t="n">
-        <v>105277</v>
+        <v>90571</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,46 +825,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224098</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ånö, Upl</t>
+          <t>Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>681999</v>
+        <v>681555</v>
       </c>
       <c r="R3" t="n">
-        <v>6683651</v>
+        <v>6683434</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,7 +895,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -906,7 +905,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,10 +933,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121993095</v>
+        <v>121993903</v>
       </c>
       <c r="B4" t="n">
-        <v>90559</v>
+        <v>90345</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,30 +945,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>5754</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -981,14 +980,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrskedika, Upl</t>
+          <t>Ånö, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>681555</v>
+        <v>681977</v>
       </c>
       <c r="R4" t="n">
-        <v>6683434</v>
+        <v>6683614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1030,7 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,10 +1057,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121993903</v>
+        <v>121992762</v>
       </c>
       <c r="B5" t="n">
-        <v>90333</v>
+        <v>56589</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1070,38 +1069,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5754</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1109,13 +1109,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>681977</v>
+        <v>681555</v>
       </c>
       <c r="R5" t="n">
-        <v>6683614</v>
+        <v>6683434</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,7 +1163,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1182,10 +1181,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121992762</v>
+        <v>121994071</v>
       </c>
       <c r="B6" t="n">
-        <v>56584</v>
+        <v>105290</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1198,35 +1197,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>224098</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1234,13 +1233,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>681555</v>
+        <v>681999</v>
       </c>
       <c r="R6" t="n">
-        <v>6683434</v>
+        <v>6683651</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1269,7 +1268,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1279,7 +1278,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,6 +1287,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>122121136</v>
       </c>
       <c r="B7" t="n">
-        <v>90333</v>
+        <v>90345</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 64564-2021 artfynd.xlsx
+++ b/artfynd/A 64564-2021 artfynd.xlsx
@@ -809,10 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121993095</v>
+        <v>121994071</v>
       </c>
       <c r="B3" t="n">
-        <v>90571</v>
+        <v>105295</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -825,45 +825,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3215</v>
+        <v>224098</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Kalktallört</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Monotropa hypophegea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Wallr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrskedika, Upl</t>
+          <t>Ånö, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>681555</v>
+        <v>681999</v>
       </c>
       <c r="R3" t="n">
-        <v>6683434</v>
+        <v>6683651</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,7 +896,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -905,7 +906,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -936,7 +937,7 @@
         <v>121993903</v>
       </c>
       <c r="B4" t="n">
-        <v>90345</v>
+        <v>90349</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1057,10 +1058,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121992762</v>
+        <v>121993095</v>
       </c>
       <c r="B5" t="n">
-        <v>56589</v>
+        <v>90575</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1073,39 +1074,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ånö, Upl</t>
+          <t>Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1115,7 +1115,7 @@
         <v>6683434</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,6 +1163,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1181,10 +1182,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121994071</v>
+        <v>121992762</v>
       </c>
       <c r="B6" t="n">
-        <v>105290</v>
+        <v>56589</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1197,35 +1198,35 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224098</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1233,13 +1234,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>681999</v>
+        <v>681555</v>
       </c>
       <c r="R6" t="n">
-        <v>6683651</v>
+        <v>6683434</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1268,7 +1269,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1278,7 +1279,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1287,7 +1288,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1309,7 +1309,7 @@
         <v>122121136</v>
       </c>
       <c r="B7" t="n">
-        <v>90345</v>
+        <v>90349</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 64564-2021 artfynd.xlsx
+++ b/artfynd/A 64564-2021 artfynd.xlsx
@@ -1309,7 +1309,7 @@
         <v>122121136</v>
       </c>
       <c r="B7" t="n">
-        <v>90349</v>
+        <v>90354</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1323,11 +1323,6 @@
       </c>
       <c r="E7" t="n">
         <v>5754</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Gultoppig fingersvamp</t>
-        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/artfynd/A 64564-2021 artfynd.xlsx
+++ b/artfynd/A 64564-2021 artfynd.xlsx
@@ -1309,7 +1309,7 @@
         <v>122121136</v>
       </c>
       <c r="B7" t="n">
-        <v>90354</v>
+        <v>90367</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1323,6 +1323,11 @@
       </c>
       <c r="E7" t="n">
         <v>5754</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/artfynd/A 64564-2021 artfynd.xlsx
+++ b/artfynd/A 64564-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97468526</v>
+        <v>56442976</v>
       </c>
       <c r="B2" t="n">
-        <v>88896</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -708,31 +703,20 @@
           <t>(Pers.) Gray</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ånö, Östhammar, Upl</t>
+          <t>Söderskogen 5,5 km NO om Hökhuvud kyrka, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>681966.6021146807</v>
+        <v>682006</v>
       </c>
       <c r="R2" t="n">
-        <v>6683664.780127225</v>
+        <v>6683463</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-08-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Två halva häxringar, 2 resp. 4 m i diameter, i vegetationsskikt av kranshakmossa, piprör och lågörter, under äldre gran, i svagt sluttande fuktstråk.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,94 +759,82 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
-      </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Blandskog med gran, tall och lövträd, främst aspar. Vissa partier med tätare skog, våtare områden och stenigare terräng.</t>
+          <t>Fuktstråk i äldre, örtrik barrskog.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Susanne Åkesson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Susanne Åkesson</t>
+          <t>Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121994071</v>
+        <v>97468526</v>
       </c>
       <c r="B3" t="n">
-        <v>105295</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224098</v>
+        <v>720</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kalktallört</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Monotropa hypophegea</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Wallr.</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ånö, Upl</t>
+          <t>Ånö, Östhammar, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>681999</v>
+        <v>681966</v>
       </c>
       <c r="R3" t="n">
-        <v>6683651</v>
+        <v>6683665</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,22 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,6 +875,16 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barr-/lövbland</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Blandskog med gran, tall och lövträd, främst aspar. Vissa partier med tätare skog, våtare områden och stenigare terräng.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -934,42 +901,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121993903</v>
+        <v>121993095</v>
       </c>
       <c r="B4" t="n">
-        <v>90349</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5754</v>
+        <v>3215</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -981,14 +943,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ånö, Upl</t>
+          <t>Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>681977</v>
+        <v>681555</v>
       </c>
       <c r="R4" t="n">
-        <v>6683614</v>
+        <v>6683434</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1020,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1030,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1058,42 +1020,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121993095</v>
+        <v>121993903</v>
       </c>
       <c r="B5" t="n">
-        <v>90575</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>5754</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1105,14 +1062,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrskedika, Upl</t>
+          <t>Ånö, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>681555</v>
+        <v>681977</v>
       </c>
       <c r="R5" t="n">
-        <v>6683434</v>
+        <v>6683614</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1154,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1182,37 +1139,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121992762</v>
+        <v>122121136</v>
       </c>
       <c r="B6" t="n">
-        <v>56589</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>5754</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1220,27 +1172,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ånö, Upl</t>
+          <t>Norrskedika, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>681555</v>
+        <v>681976</v>
       </c>
       <c r="R6" t="n">
-        <v>6683434</v>
+        <v>6683615</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1269,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1279,7 +1230,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,6 +1239,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1306,37 +1258,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122121136</v>
+        <v>121992762</v>
       </c>
       <c r="B7" t="n">
-        <v>90367</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5754</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1344,26 +1291,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norrskedika, Upl</t>
+          <t>Ånö, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>681976</v>
+        <v>681555</v>
       </c>
       <c r="R7" t="n">
-        <v>6683615</v>
+        <v>6683434</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1392,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1402,7 +1350,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1411,7 +1359,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1427,6 +1374,126 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121994071</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106231</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>224098</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kalktallört</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Monotropa hypophegea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Wallr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ånö, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>681999</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6683651</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hökhuvud</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64564-2021 artfynd.xlsx
+++ b/artfynd/A 64564-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56442976</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97468526</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,6 +1032,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121993095</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121993903</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1255,6 +1280,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122121136</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,6 +1404,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121992762</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1494,8 +1529,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121994071</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>